--- a/CSCG_rooms.xlsx
+++ b/CSCG_rooms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23d5595a8aedaea0/Desktop/sunLab/CSCG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\OneDrive\Desktop\sunLab\CSCG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{A2E4EA6A-9A94-4578-BDC0-16316EF5C145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B99287F-C894-4970-9C1C-2614568B1FC4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEAB6B4-A1D4-42B3-B321-D1F7C18DDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="16663" xr2:uid="{458C665F-2A40-4E60-A8B1-0CDDE2DB9563}"/>
   </bookViews>
@@ -402,10 +402,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FCE50A-E014-4B1E-BFB0-7FC930E73456}">
-  <dimension ref="C4:T26"/>
+  <dimension ref="C4:W26"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D4">
         <v>0</v>
       </c>
@@ -431,7 +431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D5">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D6">
         <v>0</v>
       </c>
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D7">
         <v>0</v>
       </c>
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D8">
         <v>0</v>
       </c>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D9">
         <v>0</v>
       </c>
@@ -570,7 +570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:23" x14ac:dyDescent="0.4">
       <c r="D10">
         <v>0</v>
       </c>
@@ -605,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:23" x14ac:dyDescent="0.4">
       <c r="R11">
         <v>7</v>
       </c>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="13" spans="3:23" x14ac:dyDescent="0.4">
       <c r="C13">
         <v>0</v>
       </c>
@@ -657,7 +657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="3:20" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:23" x14ac:dyDescent="0.4">
       <c r="C14">
         <v>0</v>
       </c>
@@ -698,7 +698,87 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="6:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:23" x14ac:dyDescent="0.4">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="6:23" x14ac:dyDescent="0.4">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="6:23" x14ac:dyDescent="0.4">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>-1</v>
+      </c>
+      <c r="U18">
+        <v>-1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="6:23" x14ac:dyDescent="0.4">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>-1</v>
+      </c>
+      <c r="U19">
+        <v>-1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F20">
         <v>3</v>
       </c>
@@ -714,8 +794,26 @@
       <c r="J20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="6:14" x14ac:dyDescent="0.4">
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F21">
         <v>3</v>
       </c>
@@ -731,8 +829,26 @@
       <c r="J21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="6:14" x14ac:dyDescent="0.4">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F22">
         <v>3</v>
       </c>
@@ -749,7 +865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="6:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F23">
         <v>3</v>
       </c>
@@ -766,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="6:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F24">
         <v>3</v>
       </c>
@@ -783,7 +899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="6:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="6:23" x14ac:dyDescent="0.4">
       <c r="F26">
         <v>0</v>
       </c>

--- a/CSCG_rooms.xlsx
+++ b/CSCG_rooms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\OneDrive\Desktop\sunLab\CSCG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEAB6B4-A1D4-42B3-B321-D1F7C18DDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D551919E-1FB5-46C1-BE7C-29165AF2E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="16663" xr2:uid="{458C665F-2A40-4E60-A8B1-0CDDE2DB9563}"/>
+    <workbookView xWindow="13080" yWindow="0" windowWidth="13337" windowHeight="16543" xr2:uid="{458C665F-2A40-4E60-A8B1-0CDDE2DB9563}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -700,39 +700,39 @@
     </row>
     <row r="16" spans="3:23" x14ac:dyDescent="0.4">
       <c r="R16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16">
         <v>1</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="6:23" x14ac:dyDescent="0.4">
       <c r="R17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <v>1</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17">
         <v>1</v>
@@ -740,10 +740,10 @@
     </row>
     <row r="18" spans="6:23" x14ac:dyDescent="0.4">
       <c r="R18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -752,7 +752,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18">
         <v>1</v>
@@ -760,10 +760,10 @@
     </row>
     <row r="19" spans="6:23" x14ac:dyDescent="0.4">
       <c r="R19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -772,7 +772,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19">
         <v>1</v>
@@ -795,22 +795,22 @@
         <v>3</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20">
         <v>1</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="6:23" x14ac:dyDescent="0.4">
@@ -830,22 +830,22 @@
         <v>3</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="6:23" x14ac:dyDescent="0.4">
